--- a/generated/sources/reports/apac/korea/[주간] 백화점 매출 보고_10월 3주차(10.12~10.18).xlsx
+++ b/generated/sources/reports/apac/korea/[주간] 백화점 매출 보고_10월 3주차(10.12~10.18).xlsx
@@ -186,37 +186,37 @@
     <t>매출(천원, VAT포함)</t>
   </si>
   <si>
-    <t>MAYA (마야)</t>
+    <t>NOVA (Nova)</t>
   </si>
   <si>
     <t>블랙</t>
   </si>
   <si>
-    <t>LOGO BEANIE</t>
+    <t>VLOGO BEANIE</t>
   </si>
   <si>
     <t>네이비</t>
   </si>
   <si>
-    <t>LOGO CARDIGAN</t>
-  </si>
-  <si>
-    <t>HERMINE (에르민)</t>
-  </si>
-  <si>
-    <t>TRAILGRIP W</t>
-  </si>
-  <si>
-    <t>MAIRE (마이레)</t>
-  </si>
-  <si>
-    <t>BADY (바디)</t>
-  </si>
-  <si>
-    <t>TRAILGRIP GTX</t>
-  </si>
-  <si>
-    <t>ROSIERE</t>
+    <t>VLOGO CARDIGAN</t>
+  </si>
+  <si>
+    <t>LIVIANA (Liviana)</t>
+  </si>
+  <si>
+    <t>VTRACK W</t>
+  </si>
+  <si>
+    <t>AUREA (Aurea)</t>
+  </si>
+  <si>
+    <t>ARIA (Aria)</t>
+  </si>
+  <si>
+    <t>VTRACK GTX</t>
+  </si>
+  <si>
+    <t>RIVIERA</t>
   </si>
   <si>
     <t>오프화이트</t>
@@ -225,13 +225,13 @@
     <t>이슈 및 특이사항 (10월 3주차)</t>
   </si>
   <si>
-    <t>1. 일바로(ILVARO) 인디 핑크: 10/2 이후 전 매장 품절 지속. LUMIERE 윤하은 착용 사진 이후 문의 폭주. 대기 고객 리스트 - 청담 24명, 압구정 29명, 센텀 15명 (중복 포함 가능).</t>
-  </si>
-  <si>
-    <t>2. 청담 일바로 리오더 물량: 인천세관 KC 인증서류 미비로 통관 지연, 10/8 입고 예정 -&gt; 10/13 입고. 입고 당일 대부분 대기 고객에게 판매.</t>
-  </si>
-  <si>
-    <t>3. 블랙/오프화이트 일바로도 사이즈 1, 2 결품. 본사 추가 배분 요청 중.</t>
+    <t>1. Iridia(IRIDIA) 인디 핑크: 10/2 이후 전 매장 품절 지속. LUMIERE 윤하은 착용 사진 이후 문의 폭주. 대기 고객 리스트 - 청담 24명, 압구정 29명, 센텀 15명 (중복 포함 가능).</t>
+  </si>
+  <si>
+    <t>2. 청담 Iridia 리오더 물량: 인천세관 KC 인증서류 미비로 통관 지연, 10/8 입고 예정 -&gt; 10/13 입고. 입고 당일 대부분 대기 고객에게 판매.</t>
+  </si>
+  <si>
+    <t>3. 블랙/오프화이트 Iridia도 사이즈 1, 2 결품. 본사 추가 배분 요청 중.</t>
   </si>
   <si>
     <t>4. 10/15부터 청담 플래그십 맞은편에 캐나다 아웃도어 브랜드 팝업 오픈 (대기줄, 사은품 증정). 금주 플래그십 아우터 매출 영향 있음.</t>
@@ -243,10 +243,10 @@
     <t>6. 중국 고객 매출 비중 금주 8% (POS 국적 기준).</t>
   </si>
   <si>
-    <t>7. 파리/밀라노 출장 고객으로부터 블랙 마이레(MAIRE) 현지 품절 문의 다수 - 국내 재고 문의 증가.</t>
-  </si>
-  <si>
-    <t>8. 티브(TIB) 베스트 지퍼 불량 교환 건 발생, 본사 품질팀 공유 완료.</t>
+    <t>7. 파리/밀라노 출장 고객으로부터 블랙 Aurea(AUREA) 현지 품절 문의 다수 - 국내 재고 문의 증가.</t>
+  </si>
+  <si>
+    <t>8. 티브(VEL) 베스트 지퍼 불량 교환 건 발생, 본사 품질팀 공유 완료.</t>
   </si>
   <si>
     <t>작성: 리테일팀 정다은 / 검토: 리테일팀장 오승훈 / 2026.10.19 - 대외비</t>
